--- a/pdf/Fiches-presentatives/Tableau-de-synthese-Thileli-MEBARKI.xlsx
+++ b/pdf/Fiches-presentatives/Tableau-de-synthese-Thileli-MEBARKI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents-bts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cours-SLAM1\Projets\Portfolio-3\pdf\Fiches-presentatives\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75D4516D-D085-4A2E-B600-F2967A0F59F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43FC36D2-7D75-482A-98AC-0E1B2ADC82D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="57">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t xml:space="preserve">Tableau de synthèse des réalisations professionnelles </t>
-  </si>
-  <si>
-    <t xml:space="preserve">N° candidat : </t>
   </si>
   <si>
     <t>Option :</t>
@@ -175,6 +172,63 @@
   </si>
   <si>
     <t>Projet Médiathèque</t>
+  </si>
+  <si>
+    <t>N° candidat : 02542532577</t>
+  </si>
+  <si>
+    <t>Du 03/11/2025 au 09/02/2026</t>
+  </si>
+  <si>
+    <t>Du 10/03/2025 au 01/04/2025</t>
+  </si>
+  <si>
+    <t>Du 02/09/2025 au 06/01/2026</t>
+  </si>
+  <si>
+    <t>Du 05/04/2025 au 20/04/2026</t>
+  </si>
+  <si>
+    <t>Du 12/01/2026 au 08/02/2026</t>
+  </si>
+  <si>
+    <t>Assurer la maintenance des systèmes des salles de réunion</t>
+  </si>
+  <si>
+    <t>Depuis 01/2025</t>
+  </si>
+  <si>
+    <t>Depuis 09/2024</t>
+  </si>
+  <si>
+    <t>Du 12/2024 au 05/2025</t>
+  </si>
+  <si>
+    <t>Depuis 02/2025</t>
+  </si>
+  <si>
+    <t>Depuis 09/2025</t>
+  </si>
+  <si>
+    <t>Du 10/2025 au 03/2026</t>
+  </si>
+  <si>
+    <t>Depuis 10/2025</t>
+  </si>
+  <si>
+    <t>Bibliothèque de référence "Les animaux et nous"</t>
+  </si>
+  <si>
+    <t>Du 16/12/2025 au 06/01/2026</t>
+  </si>
+  <si>
+    <t>Du 05/04/2025 au 05/10/2026</t>
+  </si>
+  <si>
+    <t>Jeu des allumettes</t>
+  </si>
+  <si>
+    <t>Du 02/03/2026 au 30/03/2026</t>
   </si>
 </sst>
 </file>
@@ -738,15 +792,42 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -779,38 +860,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1141,131 +1190,131 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="70.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" style="1" customWidth="1"/>
     <col min="3" max="8" width="18.6640625" style="1" customWidth="1"/>
     <col min="9" max="43" width="11.44140625" customWidth="1"/>
     <col min="44" max="16384" width="10.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="26"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="44" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="39"/>
-      <c r="H3" s="45"/>
+      <c r="A3" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="27"/>
+      <c r="H3" s="33"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="23" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="46"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="34" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="37"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
+      <c r="B6" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="C6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="7" t="s">
+    </row>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="35"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="19" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="19" t="s">
+      <c r="D7" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="E7" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="F7" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="G7" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="H7" s="20" t="s">
         <v>19</v>
-      </c>
-      <c r="H7" s="20" t="s">
-        <v>20</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1304,16 +1353,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
+      <c r="A8" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="38"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1352,9 +1401,11 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="8"/>
+        <v>24</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>54</v>
+      </c>
       <c r="C9" s="14"/>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
@@ -1362,9 +1413,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="15"/>
-      <c r="H9" s="22" t="b">
-        <v>1</v>
-      </c>
+      <c r="H9" s="16"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1403,14 +1452,14 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="8"/>
+        <v>25</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>40</v>
+      </c>
       <c r="C10" s="15"/>
       <c r="D10" s="15"/>
-      <c r="E10" s="21" t="b">
-        <v>1</v>
-      </c>
+      <c r="E10" s="15"/>
       <c r="F10" s="21" t="b">
         <v>1</v>
       </c>
@@ -1456,9 +1505,11 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="8"/>
+        <v>30</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>41</v>
+      </c>
       <c r="C11" s="15"/>
       <c r="D11" s="21" t="b">
         <v>1</v>
@@ -1513,9 +1564,11 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="8"/>
+        <v>31</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>39</v>
+      </c>
       <c r="C12" s="15"/>
       <c r="D12" s="21" t="b">
         <v>1</v>
@@ -1526,7 +1579,7 @@
       <c r="F12" s="21" t="b">
         <v>1</v>
       </c>
-      <c r="G12" s="46" t="b">
+      <c r="G12" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H12" s="22" t="b">
@@ -1570,18 +1623,20 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="8"/>
+        <v>32</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>42</v>
+      </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
-      <c r="E13" s="21" t="b">
-        <v>1</v>
-      </c>
+      <c r="E13" s="15"/>
       <c r="F13" s="21" t="b">
         <v>1</v>
       </c>
-      <c r="G13" s="15"/>
+      <c r="G13" s="21" t="b">
+        <v>1</v>
+      </c>
       <c r="H13" s="22" t="b">
         <v>1</v>
       </c>
@@ -1623,9 +1678,11 @@
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="8"/>
+        <v>37</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>43</v>
+      </c>
       <c r="C14" s="15"/>
       <c r="D14" s="21" t="b">
         <v>1</v>
@@ -1639,7 +1696,9 @@
       <c r="G14" s="21" t="b">
         <v>1</v>
       </c>
-      <c r="H14" s="16"/>
+      <c r="H14" s="22" t="b">
+        <v>1</v>
+      </c>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1677,14 +1736,24 @@
       <c r="AQ14"/>
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="8"/>
+      <c r="A15" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>53</v>
+      </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="16"/>
+      <c r="F15" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="22" t="b">
+        <v>1</v>
+      </c>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1722,14 +1791,24 @@
       <c r="AQ15"/>
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="8"/>
+      <c r="A16" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>56</v>
+      </c>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="16"/>
+      <c r="F16" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="22" t="b">
+        <v>1</v>
+      </c>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1857,16 +1936,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A19" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="32"/>
+      <c r="A19" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="41"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1905,9 +1984,11 @@
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="8"/>
+        <v>28</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>47</v>
+      </c>
       <c r="C20" s="21" t="b">
         <v>1</v>
       </c>
@@ -1960,9 +2041,11 @@
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="8"/>
+        <v>23</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>45</v>
+      </c>
       <c r="C21" s="21" t="b">
         <v>1</v>
       </c>
@@ -2015,9 +2098,11 @@
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="8"/>
+        <v>33</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>46</v>
+      </c>
       <c r="C22" s="21" t="b">
         <v>1</v>
       </c>
@@ -2249,16 +2334,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A27" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="31"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="32"/>
+      <c r="A27" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="40"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="41"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2297,9 +2382,11 @@
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="8"/>
+        <v>29</v>
+      </c>
+      <c r="B28" s="24" t="s">
+        <v>49</v>
+      </c>
       <c r="C28" s="21" t="b">
         <v>1</v>
       </c>
@@ -2352,9 +2439,11 @@
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="46.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="8"/>
+        <v>27</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>48</v>
+      </c>
       <c r="C29" s="21" t="b">
         <v>1</v>
       </c>
@@ -2407,9 +2496,11 @@
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="8"/>
+        <v>33</v>
+      </c>
+      <c r="B30" s="24" t="s">
+        <v>46</v>
+      </c>
       <c r="C30" s="21" t="b">
         <v>1</v>
       </c>
@@ -2462,17 +2553,23 @@
     </row>
     <row r="31" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" s="8"/>
+        <v>26</v>
+      </c>
+      <c r="B31" s="24" t="s">
+        <v>50</v>
+      </c>
       <c r="C31" s="21" t="b">
         <v>1</v>
       </c>
       <c r="D31" s="21" t="b">
         <v>1</v>
       </c>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
+      <c r="E31" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" s="21" t="b">
+        <v>1</v>
+      </c>
       <c r="G31" s="21" t="b">
         <v>1</v>
       </c>
@@ -2516,14 +2613,26 @@
       <c r="AQ31"/>
     </row>
     <row r="32" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="9"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
+      <c r="A32" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D32" s="21" t="b">
+        <v>1</v>
+      </c>
       <c r="E32" s="15"/>
       <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="16"/>
+      <c r="G32" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="22" t="b">
+        <v>1</v>
+      </c>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
@@ -2743,11 +2852,6 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2755,6 +2859,11 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2765,12 +2874,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ReferenceId xmlns="eb611b18-53d2-4338-873f-1a24be3de2f9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2900,17 +3008,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ReferenceId xmlns="eb611b18-53d2-4338-873f-1a24be3de2f9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDBF46EB-2966-443D-80D8-C65B63215F7D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D66614C4-909C-4B97-87F7-8E1DA6E86ED4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eb611b18-53d2-4338-873f-1a24be3de2f9"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2934,11 +3045,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D66614C4-909C-4B97-87F7-8E1DA6E86ED4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDBF46EB-2966-443D-80D8-C65B63215F7D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eb611b18-53d2-4338-873f-1a24be3de2f9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/pdf/Fiches-presentatives/Tableau-de-synthese-Thileli-MEBARKI.xlsx
+++ b/pdf/Fiches-presentatives/Tableau-de-synthese-Thileli-MEBARKI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cours-SLAM1\Projets\Portfolio-3\pdf\Fiches-presentatives\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43FC36D2-7D75-482A-98AC-0E1B2ADC82D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A725A0F-C94D-4593-BDD7-D40B618ACD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$33</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -1186,7 +1186,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ81"/>
+  <dimension ref="A1:AQ79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="70.44140625" style="1" customWidth="1"/>
@@ -1510,7 +1510,9 @@
       <c r="B11" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="15"/>
+      <c r="C11" s="21" t="b">
+        <v>1</v>
+      </c>
       <c r="D11" s="21" t="b">
         <v>1</v>
       </c>
@@ -1569,7 +1571,9 @@
       <c r="B12" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="15"/>
+      <c r="C12" s="21" t="b">
+        <v>1</v>
+      </c>
       <c r="D12" s="21" t="b">
         <v>1</v>
       </c>
@@ -1683,7 +1687,9 @@
       <c r="B14" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="15"/>
+      <c r="C14" s="21" t="b">
+        <v>1</v>
+      </c>
       <c r="D14" s="21" t="b">
         <v>1</v>
       </c>
@@ -1742,7 +1748,9 @@
       <c r="B15" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="15"/>
+      <c r="C15" s="21" t="b">
+        <v>1</v>
+      </c>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
       <c r="F15" s="21" t="b">
@@ -1797,7 +1805,9 @@
       <c r="B16" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="15"/>
+      <c r="C16" s="21" t="b">
+        <v>1</v>
+      </c>
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
       <c r="F16" s="21" t="b">
@@ -1996,7 +2006,9 @@
         <v>1</v>
       </c>
       <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
+      <c r="F20" s="21" t="b">
+        <v>1</v>
+      </c>
       <c r="G20" s="21" t="b">
         <v>1</v>
       </c>
@@ -2052,8 +2064,12 @@
       <c r="D21" s="21" t="b">
         <v>1</v>
       </c>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
+      <c r="E21" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" s="21" t="b">
+        <v>1</v>
+      </c>
       <c r="G21" s="21" t="b">
         <v>1</v>
       </c>
@@ -2243,15 +2259,17 @@
       <c r="AP24"/>
       <c r="AQ24"/>
     </row>
-    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="9"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="16"/>
+    <row r="25" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A25" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="40"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="41"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -2289,14 +2307,28 @@
       <c r="AQ25"/>
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="9"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
+      <c r="A26" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D26" s="21" t="b">
+        <v>1</v>
+      </c>
       <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="16"/>
+      <c r="F26" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" s="22" t="b">
+        <v>1</v>
+      </c>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2333,17 +2365,29 @@
       <c r="AP26"/>
       <c r="AQ26"/>
     </row>
-    <row r="27" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A27" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27" s="40"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="41"/>
+    <row r="27" spans="1:43" s="2" customFormat="1" ht="46.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D27" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" s="15"/>
+      <c r="G27" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" s="22" t="b">
+        <v>1</v>
+      </c>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2382,10 +2426,10 @@
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C28" s="21" t="b">
         <v>1</v>
@@ -2437,12 +2481,12 @@
       <c r="AP28"/>
       <c r="AQ28"/>
     </row>
-    <row r="29" spans="1:43" s="2" customFormat="1" ht="46.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C29" s="21" t="b">
         <v>1</v>
@@ -2450,8 +2494,12 @@
       <c r="D29" s="21" t="b">
         <v>1</v>
       </c>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
+      <c r="E29" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" s="21" t="b">
+        <v>1</v>
+      </c>
       <c r="G29" s="21" t="b">
         <v>1</v>
       </c>
@@ -2496,10 +2544,10 @@
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C30" s="21" t="b">
         <v>1</v>
@@ -2508,7 +2556,9 @@
         <v>1</v>
       </c>
       <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
+      <c r="F30" s="21" t="b">
+        <v>1</v>
+      </c>
       <c r="G30" s="21" t="b">
         <v>1</v>
       </c>
@@ -2552,30 +2602,14 @@
       <c r="AQ30"/>
     </row>
     <row r="31" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C31" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="D31" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="F31" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="22" t="b">
-        <v>1</v>
-      </c>
+      <c r="A31" s="9"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="16"/>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
@@ -2612,27 +2646,15 @@
       <c r="AP31"/>
       <c r="AQ31"/>
     </row>
-    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="D32" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="22" t="b">
-        <v>1</v>
-      </c>
+    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="10"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="18"/>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
@@ -2669,15 +2691,15 @@
       <c r="AP32"/>
       <c r="AQ32"/>
     </row>
-    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="9"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="16"/>
+    <row r="33" spans="1:43" s="2" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A33" s="5"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
       <c r="I33"/>
       <c r="J33"/>
       <c r="K33"/>
@@ -2714,96 +2736,8 @@
       <c r="AP33"/>
       <c r="AQ33"/>
     </row>
-    <row r="34" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="10"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="18"/>
-      <c r="I34"/>
-      <c r="J34"/>
-      <c r="K34"/>
-      <c r="L34"/>
-      <c r="M34"/>
-      <c r="N34"/>
-      <c r="O34"/>
-      <c r="P34"/>
-      <c r="Q34"/>
-      <c r="R34"/>
-      <c r="S34"/>
-      <c r="T34"/>
-      <c r="U34"/>
-      <c r="V34"/>
-      <c r="W34"/>
-      <c r="X34"/>
-      <c r="Y34"/>
-      <c r="Z34"/>
-      <c r="AA34"/>
-      <c r="AB34"/>
-      <c r="AC34"/>
-      <c r="AD34"/>
-      <c r="AE34"/>
-      <c r="AF34"/>
-      <c r="AG34"/>
-      <c r="AH34"/>
-      <c r="AI34"/>
-      <c r="AJ34"/>
-      <c r="AK34"/>
-      <c r="AL34"/>
-      <c r="AM34"/>
-      <c r="AN34"/>
-      <c r="AO34"/>
-      <c r="AP34"/>
-      <c r="AQ34"/>
-    </row>
-    <row r="35" spans="1:43" s="2" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A35" s="5"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35"/>
-      <c r="J35"/>
-      <c r="K35"/>
-      <c r="L35"/>
-      <c r="M35"/>
-      <c r="N35"/>
-      <c r="O35"/>
-      <c r="P35"/>
-      <c r="Q35"/>
-      <c r="R35"/>
-      <c r="S35"/>
-      <c r="T35"/>
-      <c r="U35"/>
-      <c r="V35"/>
-      <c r="W35"/>
-      <c r="X35"/>
-      <c r="Y35"/>
-      <c r="Z35"/>
-      <c r="AA35"/>
-      <c r="AB35"/>
-      <c r="AC35"/>
-      <c r="AD35"/>
-      <c r="AE35"/>
-      <c r="AF35"/>
-      <c r="AG35"/>
-      <c r="AH35"/>
-      <c r="AI35"/>
-      <c r="AJ35"/>
-      <c r="AK35"/>
-      <c r="AL35"/>
-      <c r="AM35"/>
-      <c r="AN35"/>
-      <c r="AO35"/>
-      <c r="AP35"/>
-      <c r="AQ35"/>
-    </row>
+    <row r="34" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -2848,15 +2782,13 @@
     <row r="77" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="78" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="79" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="80" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="G1:H1"/>

--- a/pdf/Fiches-presentatives/Tableau-de-synthese-Thileli-MEBARKI.xlsx
+++ b/pdf/Fiches-presentatives/Tableau-de-synthese-Thileli-MEBARKI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thile\OneDrive\Bureau\tableau-de-synthèse-version-finale\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E76A66C-9C8D-4AD8-A92A-7A77D256A70A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F34DA1A-C303-40D4-9B78-4E65C2054366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$27</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -162,9 +162,6 @@
     <t>Du 12/01/2026 au 08/02/2026</t>
   </si>
   <si>
-    <t>Assurer la maintenance des systèmes des salles de réunion</t>
-  </si>
-  <si>
     <t>Depuis 01/2025</t>
   </si>
   <si>
@@ -180,12 +177,6 @@
     <t>Bibliothèque de référence "Les animaux et nous"</t>
   </si>
   <si>
-    <t>Jeu des allumettes</t>
-  </si>
-  <si>
-    <t>Du 02/03/2026 au 30/03/2026</t>
-  </si>
-  <si>
     <t>Du 09/2025 au 01/2026</t>
   </si>
   <si>
@@ -201,9 +192,6 @@
     <t>Du 16/12/2025 au 19/01/2026</t>
   </si>
   <si>
-    <t>Centre de formation : Insta</t>
-  </si>
-  <si>
     <t>Depuis 05/2025</t>
   </si>
   <si>
@@ -222,13 +210,19 @@
     <t>Remplacements des MTR des salles de réunion</t>
   </si>
   <si>
+    <t>Assurer la maintenance des systèmes de visioconférence</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio : https://thilelimebarki.github.io/Portfolio/</t>
+  </si>
+  <si>
+    <t>Centre de formation : INSTA</t>
+  </si>
+  <si>
+    <t>NOM et prénom :  MEBARKI Thileli</t>
+  </si>
+  <si>
     <t>N° candidat : 02542532577</t>
-  </si>
-  <si>
-    <t>NOM et prénom :  MEBARKI Thileli</t>
-  </si>
-  <si>
-    <t>Adresse URL du portfolio : https://thilelimebarki.github.io/Portfolio/</t>
   </si>
 </sst>
 </file>
@@ -1120,7 +1114,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ74"/>
+  <dimension ref="A1:AQ73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="70.44140625" style="1" customWidth="1"/>
@@ -1158,7 +1152,7 @@
     </row>
     <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B3" s="20"/>
       <c r="C3" s="20"/>
@@ -1175,7 +1169,7 @@
     </row>
     <row r="4" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B4" s="23"/>
       <c r="C4" s="23"/>
@@ -1193,7 +1187,7 @@
     </row>
     <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="37" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B5" s="38"/>
       <c r="C5" s="38"/>
@@ -1338,16 +1332,16 @@
         <v>23</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
-      <c r="F9" s="14" t="b">
-        <v>1</v>
-      </c>
+      <c r="F9" s="10"/>
       <c r="G9" s="10"/>
-      <c r="H9" s="11"/>
+      <c r="H9" s="15" t="b">
+        <v>1</v>
+      </c>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1393,15 +1387,11 @@
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
-      <c r="E10" s="14" t="b">
-        <v>1</v>
-      </c>
+      <c r="E10" s="10"/>
       <c r="F10" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="G10" s="14" t="b">
-        <v>1</v>
-      </c>
+      <c r="G10" s="10"/>
       <c r="H10" s="15" t="b">
         <v>1</v>
       </c>
@@ -1446,7 +1436,7 @@
         <v>28</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
@@ -1454,9 +1444,7 @@
       <c r="F11" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="G11" s="14" t="b">
-        <v>1</v>
-      </c>
+      <c r="G11" s="10"/>
       <c r="H11" s="15" t="b">
         <v>1</v>
       </c>
@@ -1498,7 +1486,7 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>32</v>
@@ -1506,12 +1494,8 @@
       <c r="C12" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="D12" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="14" t="b">
-        <v>1</v>
-      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
       <c r="F12" s="14" t="b">
         <v>1</v>
       </c>
@@ -1567,12 +1551,8 @@
       <c r="C13" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="D13" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="14" t="b">
-        <v>1</v>
-      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
       <c r="F13" s="14" t="b">
         <v>1</v>
       </c>
@@ -1620,22 +1600,18 @@
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="14" t="b">
-        <v>1</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="C14" s="10"/>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
       <c r="F14" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="G14" s="14" t="b">
-        <v>1</v>
-      </c>
+      <c r="G14" s="10"/>
       <c r="H14" s="15" t="b">
         <v>1</v>
       </c>
@@ -1685,12 +1661,8 @@
       <c r="C15" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="D15" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14" t="b">
-        <v>1</v>
-      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
       <c r="F15" s="14" t="b">
         <v>1</v>
       </c>
@@ -1737,24 +1709,14 @@
       <c r="AQ15"/>
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>41</v>
-      </c>
+      <c r="A16" s="6"/>
+      <c r="B16" s="5"/>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
-      <c r="F16" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" s="15" t="b">
-        <v>1</v>
-      </c>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="11"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1791,15 +1753,17 @@
       <c r="AP16"/>
       <c r="AQ16"/>
     </row>
-    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="11"/>
+    <row r="17" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A17" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="34"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1836,17 +1800,23 @@
       <c r="AP17"/>
       <c r="AQ17"/>
     </row>
-    <row r="18" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A18" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="34"/>
+    <row r="18" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="10"/>
+      <c r="D18" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="11"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1885,10 +1855,10 @@
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C19" s="14" t="b">
         <v>1</v>
@@ -1897,10 +1867,10 @@
         <v>1</v>
       </c>
       <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="14" t="b">
-        <v>1</v>
-      </c>
+      <c r="F19" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" s="10"/>
       <c r="H19" s="15" t="b">
         <v>1</v>
       </c>
@@ -1942,10 +1912,10 @@
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C20" s="14" t="b">
         <v>1</v>
@@ -1957,12 +1927,8 @@
       <c r="F20" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="G20" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20" s="15" t="b">
-        <v>1</v>
-      </c>
+      <c r="G20" s="10"/>
+      <c r="H20" s="11"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -2000,28 +1966,14 @@
       <c r="AQ20"/>
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D21" s="14" t="b">
-        <v>1</v>
-      </c>
+      <c r="A21" s="6"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
       <c r="E21" s="10"/>
-      <c r="F21" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G21" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H21" s="15" t="b">
-        <v>1</v>
-      </c>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="11"/>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
@@ -2058,15 +2010,17 @@
       <c r="AP21"/>
       <c r="AQ21"/>
     </row>
-    <row r="22" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="11"/>
+    <row r="22" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A22" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="34"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -2103,17 +2057,25 @@
       <c r="AP22"/>
       <c r="AQ22"/>
     </row>
-    <row r="23" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A23" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="33"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="34"/>
+    <row r="23" spans="1:43" s="2" customFormat="1" ht="46.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" s="11"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -2150,12 +2112,12 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="2" customFormat="1" ht="46.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C24" s="14" t="b">
         <v>1</v>
@@ -2164,13 +2126,11 @@
         <v>1</v>
       </c>
       <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H24" s="15" t="b">
-        <v>1</v>
-      </c>
+      <c r="F24" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" s="10"/>
+      <c r="H24" s="11"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2209,10 +2169,10 @@
     </row>
     <row r="25" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C25" s="14" t="b">
         <v>1</v>
@@ -2227,9 +2187,7 @@
       <c r="G25" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="H25" s="15" t="b">
-        <v>1</v>
-      </c>
+      <c r="H25" s="11"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -2268,29 +2226,23 @@
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B26" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="14" t="b">
-        <v>1</v>
-      </c>
+      <c r="C26" s="10"/>
       <c r="D26" s="14" t="b">
         <v>1</v>
       </c>
       <c r="E26" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="F26" s="14" t="b">
-        <v>1</v>
-      </c>
+      <c r="F26" s="10"/>
       <c r="G26" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="H26" s="15" t="b">
-        <v>1</v>
-      </c>
+      <c r="H26" s="11"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2328,30 +2280,14 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C27" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F27" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G27" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15" t="b">
-        <v>1</v>
-      </c>
+      <c r="A27" s="6"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="11"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2388,51 +2324,7 @@
       <c r="AP27"/>
       <c r="AQ27"/>
     </row>
-    <row r="28" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="6"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="11"/>
-      <c r="I28"/>
-      <c r="J28"/>
-      <c r="K28"/>
-      <c r="L28"/>
-      <c r="M28"/>
-      <c r="N28"/>
-      <c r="O28"/>
-      <c r="P28"/>
-      <c r="Q28"/>
-      <c r="R28"/>
-      <c r="S28"/>
-      <c r="T28"/>
-      <c r="U28"/>
-      <c r="V28"/>
-      <c r="W28"/>
-      <c r="X28"/>
-      <c r="Y28"/>
-      <c r="Z28"/>
-      <c r="AA28"/>
-      <c r="AB28"/>
-      <c r="AC28"/>
-      <c r="AD28"/>
-      <c r="AE28"/>
-      <c r="AF28"/>
-      <c r="AG28"/>
-      <c r="AH28"/>
-      <c r="AI28"/>
-      <c r="AJ28"/>
-      <c r="AK28"/>
-      <c r="AL28"/>
-      <c r="AM28"/>
-      <c r="AN28"/>
-      <c r="AO28"/>
-      <c r="AP28"/>
-      <c r="AQ28"/>
-    </row>
+    <row r="28" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="29" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="31" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -2478,14 +2370,13 @@
     <row r="71" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="72" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="73" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="74" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A22:H22"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="G1:H1"/>
